--- a/src/data_update/update_cards.xlsx
+++ b/src/data_update/update_cards.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,12 +17,19 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <color theme="10"/>
+      <sz val="12"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -43,14 +50,17 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="Hyperlink" xfId="1" builtinId="8" hidden="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
@@ -413,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E1"/>
+  <dimension ref="A1:E4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -443,7 +453,78 @@
         </is>
       </c>
     </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>MANTA-30813</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Manta</t>
+        </is>
+      </c>
+      <c r="C2" s="1" t="inlineStr">
+        <is>
+          <t>https://carboncars.atlassian.net/browse/MANTA-30813</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>REBLINDAGEM - 1042448 - SUPPLY 114133</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>MANTA-29816</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Manta</t>
+        </is>
+      </c>
+      <c r="C3" s="1" t="inlineStr">
+        <is>
+          <t>https://carboncars.atlassian.net/browse/MANTA-29816</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>30303</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>MANTA-29792</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Manta</t>
+        </is>
+      </c>
+      <c r="C4" s="1" t="inlineStr">
+        <is>
+          <t>https://carboncars.atlassian.net/browse/MANTA-29792</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>30282</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C4" r:id="rId3"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/src/data_update/update_cards.xlsx
+++ b/src/data_update/update_cards.xlsx
@@ -1,44 +1,197 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr/>
-  <workbookProtection/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\guarino.silva\Documents\Maestro\src\data_update\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{49C2A73A-E042-4013-B9A6-659915C80B44}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="41">
+  <si>
+    <t>ID</t>
+  </si>
+  <si>
+    <t>Tipo de issue</t>
+  </si>
+  <si>
+    <t>Chave</t>
+  </si>
+  <si>
+    <t>Resumo</t>
+  </si>
+  <si>
+    <t>DT. PREVISÃO ENTREGA</t>
+  </si>
+  <si>
+    <t>MANTA-30813</t>
+  </si>
+  <si>
+    <t>Manta</t>
+  </si>
+  <si>
+    <t>https://carboncars.atlassian.net/browse/MANTA-30813</t>
+  </si>
+  <si>
+    <t>REBLINDAGEM - 1042448 - SUPPLY 114133</t>
+  </si>
+  <si>
+    <t>10/03/2026</t>
+  </si>
+  <si>
+    <t>MANTA-30781</t>
+  </si>
+  <si>
+    <t>https://carboncars.atlassian.net/browse/MANTA-30781</t>
+  </si>
+  <si>
+    <t>30911 PED AVULSO</t>
+  </si>
+  <si>
+    <t>MANTA-30597</t>
+  </si>
+  <si>
+    <t>https://carboncars.atlassian.net/browse/MANTA-30597</t>
+  </si>
+  <si>
+    <t>31003</t>
+  </si>
+  <si>
+    <t>MANTA-30589</t>
+  </si>
+  <si>
+    <t>https://carboncars.atlassian.net/browse/MANTA-30589</t>
+  </si>
+  <si>
+    <t>30995</t>
+  </si>
+  <si>
+    <t>MANTA-30588</t>
+  </si>
+  <si>
+    <t>https://carboncars.atlassian.net/browse/MANTA-30588</t>
+  </si>
+  <si>
+    <t>30994</t>
+  </si>
+  <si>
+    <t>MANTA-30521</t>
+  </si>
+  <si>
+    <t>https://carboncars.atlassian.net/browse/MANTA-30521</t>
+  </si>
+  <si>
+    <t>30930</t>
+  </si>
+  <si>
+    <t>MANTA-30515</t>
+  </si>
+  <si>
+    <t>https://carboncars.atlassian.net/browse/MANTA-30515</t>
+  </si>
+  <si>
+    <t>30924</t>
+  </si>
+  <si>
+    <t>MANTA-30514</t>
+  </si>
+  <si>
+    <t>https://carboncars.atlassian.net/browse/MANTA-30514</t>
+  </si>
+  <si>
+    <t>30923</t>
+  </si>
+  <si>
+    <t>MANTA-30510</t>
+  </si>
+  <si>
+    <t>https://carboncars.atlassian.net/browse/MANTA-30510</t>
+  </si>
+  <si>
+    <t>30919</t>
+  </si>
+  <si>
+    <t>MANTA-30507</t>
+  </si>
+  <si>
+    <t>https://carboncars.atlassian.net/browse/MANTA-30507</t>
+  </si>
+  <si>
+    <t>30916</t>
+  </si>
+  <si>
+    <t>MANTA-30506</t>
+  </si>
+  <si>
+    <t>https://carboncars.atlassian.net/browse/MANTA-30506</t>
+  </si>
+  <si>
+    <t>30915</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  </t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <color theme="1"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color theme="0"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
       <color theme="10"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="12"/>
+      <color theme="0"/>
+      <name val="Calibri"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
-      <patternFill/>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF00B050"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -52,85 +205,27 @@
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="1"/>
+  <cellXfs count="3">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="2">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
-    <cellStyle name="Hyperlink" xfId="1" builtinId="8" hidden="0"/>
+    <cellStyle name="Hiperlink" xfId="1" builtinId="8"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -418,112 +513,237 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:E4"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:G12"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="12.90625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="51.6328125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="36.1796875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="21.08984375" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>ID</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>Tipo de issue</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>Chave</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>Resumo</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>DT. PREVISÃO ENTREGA</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>MANTA-30813</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>Manta</t>
-        </is>
-      </c>
-      <c r="C2" s="1" t="inlineStr">
-        <is>
-          <t>https://carboncars.atlassian.net/browse/MANTA-30813</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>REBLINDAGEM - 1042448 - SUPPLY 114133</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>MANTA-29816</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>Manta</t>
-        </is>
-      </c>
-      <c r="C3" s="1" t="inlineStr">
-        <is>
-          <t>https://carboncars.atlassian.net/browse/MANTA-29816</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>30303</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>MANTA-29792</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Manta</t>
-        </is>
-      </c>
-      <c r="C4" s="1" t="inlineStr">
-        <is>
-          <t>https://carboncars.atlassian.net/browse/MANTA-29792</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>30282</t>
-        </is>
+    <row r="1" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A2" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A3" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A4" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A5" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A6" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="E6" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A7" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="E7" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A8" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="E8" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="G8" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A9" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="E9" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A10" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="D10" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="E10" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A11" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="D11" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="E11" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A12" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="D12" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="E12" s="1" t="s">
+        <v>9</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C2" r:id="rId1"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C3" r:id="rId2"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C4" r:id="rId3"/>
+    <hyperlink ref="C2" r:id="rId1" xr:uid="{5713A3A5-2C19-4A78-8C43-0D4E38E49237}"/>
+    <hyperlink ref="C3" r:id="rId2" xr:uid="{D4C6954E-E655-42FE-AE39-06720AE44F45}"/>
+    <hyperlink ref="C4" r:id="rId3" xr:uid="{50D8EC11-53E8-444B-BC37-5E889A24664A}"/>
+    <hyperlink ref="C5" r:id="rId4" xr:uid="{DD77E666-C132-433F-B326-DD1F31EC8CC9}"/>
+    <hyperlink ref="C6" r:id="rId5" xr:uid="{5BF1A969-76EB-4448-A72F-ED2AE962F6E7}"/>
+    <hyperlink ref="C7" r:id="rId6" xr:uid="{7E946DA9-2CB4-49AC-9D77-FEA73A769E1F}"/>
+    <hyperlink ref="C8" r:id="rId7" xr:uid="{9FFA2A2B-9C7A-48D6-9F0B-4AB765A9833C}"/>
+    <hyperlink ref="C9" r:id="rId8" xr:uid="{0F0067F5-A37C-40E0-886D-BD174F747833}"/>
+    <hyperlink ref="C10" r:id="rId9" xr:uid="{E721F0F4-74CB-44F9-BDAC-4CD2532F8170}"/>
+    <hyperlink ref="C11" r:id="rId10" xr:uid="{260B1BFE-B770-47EE-B9A1-603601DEDFB1}"/>
+    <hyperlink ref="C12" r:id="rId11" xr:uid="{AA146BDE-AFE4-45CE-9E52-57A0122A39A2}"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/src/data_update/update_cards.xlsx
+++ b/src/data_update/update_cards.xlsx
@@ -1,44 +1,170 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr/>
-  <workbookProtection/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\guarino.silva\Documents\Maestro\src\data_update\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9BD53DA4-FE15-4ACB-872F-65165DE07346}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="34">
+  <si>
+    <t>ID</t>
+  </si>
+  <si>
+    <t>Tipo de issue</t>
+  </si>
+  <si>
+    <t>Chave</t>
+  </si>
+  <si>
+    <t>Resumo</t>
+  </si>
+  <si>
+    <t>DT. PREVISÃO ENTREGA</t>
+  </si>
+  <si>
+    <t>MANTA-30191</t>
+  </si>
+  <si>
+    <t>Manta</t>
+  </si>
+  <si>
+    <t>https://carboncars.atlassian.net/browse/MANTA-30191</t>
+  </si>
+  <si>
+    <t>MANTA-30242</t>
+  </si>
+  <si>
+    <t>https://carboncars.atlassian.net/browse/MANTA-30242</t>
+  </si>
+  <si>
+    <t>MANTA-30463</t>
+  </si>
+  <si>
+    <t>https://carboncars.atlassian.net/browse/MANTA-30463</t>
+  </si>
+  <si>
+    <t>MANTA-30428</t>
+  </si>
+  <si>
+    <t>https://carboncars.atlassian.net/browse/MANTA-30428</t>
+  </si>
+  <si>
+    <t>MANTA-30421</t>
+  </si>
+  <si>
+    <t>https://carboncars.atlassian.net/browse/MANTA-30421</t>
+  </si>
+  <si>
+    <t>MANTA-30420</t>
+  </si>
+  <si>
+    <t>https://carboncars.atlassian.net/browse/MANTA-30420</t>
+  </si>
+  <si>
+    <t>MANTA-30367</t>
+  </si>
+  <si>
+    <t>https://carboncars.atlassian.net/browse/MANTA-30367</t>
+  </si>
+  <si>
+    <t>MANTA-30196</t>
+  </si>
+  <si>
+    <t>https://carboncars.atlassian.net/browse/MANTA-30196</t>
+  </si>
+  <si>
+    <t>MANTA-29372</t>
+  </si>
+  <si>
+    <t>https://carboncars.atlassian.net/browse/MANTA-29372</t>
+  </si>
+  <si>
+    <t>MANTA-29923</t>
+  </si>
+  <si>
+    <t>https://carboncars.atlassian.net/browse/MANTA-29923</t>
+  </si>
+  <si>
+    <t>MANTA-30781</t>
+  </si>
+  <si>
+    <t>https://carboncars.atlassian.net/browse/MANTA-30781</t>
+  </si>
+  <si>
+    <t>30911 PED AVULSO</t>
+  </si>
+  <si>
+    <t>MANTA-30813</t>
+  </si>
+  <si>
+    <t>https://carboncars.atlassian.net/browse/MANTA-30813</t>
+  </si>
+  <si>
+    <t>REBLINDAGEM - 1042448 - SUPPLY 114133</t>
+  </si>
+  <si>
+    <t>10/03/2026</t>
+  </si>
+  <si>
+    <t>13/03/2026</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <color theme="1"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="0"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
       <color theme="10"/>
-      <sz val="12"/>
+      <name val="Calibri"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
-      <patternFill/>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF00B050"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -52,85 +178,27 @@
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="1"/>
+  <cellXfs count="3">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="2">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
-    <cellStyle name="Hyperlink" xfId="1" builtinId="8" hidden="0"/>
+    <cellStyle name="Hiperlink" xfId="1" builtinId="8"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -418,89 +486,253 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:E3"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:E13"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="12.90625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.6328125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="48.1796875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="36.36328125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="33.90625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="10.453125" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>ID</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>Tipo de issue</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>Chave</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>Resumo</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>DT. PREVISÃO ENTREGA</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>MANTA-29816</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>Manta</t>
-        </is>
-      </c>
-      <c r="C2" s="1" t="inlineStr">
-        <is>
-          <t>https://carboncars.atlassian.net/browse/MANTA-29816</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>30303</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>MANTA-29792</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>Manta</t>
-        </is>
-      </c>
-      <c r="C3" s="1" t="inlineStr">
-        <is>
-          <t>https://carboncars.atlassian.net/browse/MANTA-29792</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>30282</t>
-        </is>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D2" s="2">
+        <v>30628</v>
+      </c>
+      <c r="E2" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="D3" s="2">
+        <v>30674</v>
+      </c>
+      <c r="E3" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A4" t="s">
+        <v>10</v>
+      </c>
+      <c r="B4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D4" s="2">
+        <v>30876</v>
+      </c>
+      <c r="E4" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A5" t="s">
+        <v>12</v>
+      </c>
+      <c r="B5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="D5" s="2">
+        <v>30841</v>
+      </c>
+      <c r="E5" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A6" t="s">
+        <v>14</v>
+      </c>
+      <c r="B6" t="s">
+        <v>6</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D6" s="2">
+        <v>30834</v>
+      </c>
+      <c r="E6" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A7" t="s">
+        <v>16</v>
+      </c>
+      <c r="B7" t="s">
+        <v>6</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D7" s="2">
+        <v>30833</v>
+      </c>
+      <c r="E7" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A8" t="s">
+        <v>18</v>
+      </c>
+      <c r="B8" t="s">
+        <v>6</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D8" s="2">
+        <v>30786</v>
+      </c>
+      <c r="E8" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A9" t="s">
+        <v>20</v>
+      </c>
+      <c r="B9" t="s">
+        <v>6</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="D9" s="2">
+        <v>30632</v>
+      </c>
+      <c r="E9" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A10" t="s">
+        <v>22</v>
+      </c>
+      <c r="B10" t="s">
+        <v>6</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="D10" s="2">
+        <v>29901</v>
+      </c>
+      <c r="E10" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A11" t="s">
+        <v>24</v>
+      </c>
+      <c r="B11" t="s">
+        <v>6</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="D11" s="2">
+        <v>30392</v>
+      </c>
+      <c r="E11" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A12" t="s">
+        <v>26</v>
+      </c>
+      <c r="B12" t="s">
+        <v>6</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="E12" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A13" t="s">
+        <v>29</v>
+      </c>
+      <c r="B13" t="s">
+        <v>6</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="E13" t="s">
+        <v>32</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C2" r:id="rId1"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C3" r:id="rId2"/>
+    <hyperlink ref="C13" r:id="rId1" xr:uid="{48220436-EFDD-49C5-BAB6-3C732F8B2D48}"/>
+    <hyperlink ref="C12" r:id="rId2" xr:uid="{8A8F3FE6-6AB9-4BCA-9A57-30861772C4C1}"/>
+    <hyperlink ref="C4" r:id="rId3" xr:uid="{E0A505C3-AC93-41DE-9BE0-56431F0572D0}"/>
+    <hyperlink ref="C5" r:id="rId4" xr:uid="{FF372BC3-CEED-45BB-BC3C-B34E37CAF905}"/>
+    <hyperlink ref="C6" r:id="rId5" xr:uid="{98AB2DE2-C1FF-4616-931D-974005B39BF7}"/>
+    <hyperlink ref="C7" r:id="rId6" xr:uid="{CF403FB0-9EC4-4A79-A4C0-8E1AE1ECF562}"/>
+    <hyperlink ref="C8" r:id="rId7" xr:uid="{6009890C-01B2-4866-B7A5-F9205D8C684A}"/>
+    <hyperlink ref="C3" r:id="rId8" xr:uid="{9E4E93FE-86FC-4C53-BDFE-35C066C94551}"/>
+    <hyperlink ref="C9" r:id="rId9" xr:uid="{AF236D5E-A1FA-4F15-8BAB-F0B9B0B2E4F8}"/>
+    <hyperlink ref="C2" r:id="rId10" xr:uid="{FCAA7AEF-8D0D-41B1-BDFD-0794843AC37B}"/>
+    <hyperlink ref="C11" r:id="rId11" xr:uid="{01A86692-C58F-4457-AF5D-1B36E87BB340}"/>
+    <hyperlink ref="C10" r:id="rId12" xr:uid="{CF6FF52A-8E0D-471E-9880-A4D76FD5A83C}"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/src/data_update/update_cards.xlsx
+++ b/src/data_update/update_cards.xlsx
@@ -17,12 +17,19 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <color theme="10"/>
+      <sz val="12"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -43,14 +50,17 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="Hyperlink" xfId="1" builtinId="8" hidden="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
@@ -413,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E1"/>
+  <dimension ref="A1:E21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -443,7 +453,469 @@
         </is>
       </c>
     </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>MANTA-30759</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Manta</t>
+        </is>
+      </c>
+      <c r="C2" s="1" t="inlineStr">
+        <is>
+          <t>https://carboncars.atlassian.net/browse/MANTA-30759</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>30993 - ALT</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>MANTA-30722</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Manta</t>
+        </is>
+      </c>
+      <c r="C3" s="1" t="inlineStr">
+        <is>
+          <t>https://carboncars.atlassian.net/browse/MANTA-30722</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>31122</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>MANTA-30670</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Manta</t>
+        </is>
+      </c>
+      <c r="C4" s="1" t="inlineStr">
+        <is>
+          <t>https://carboncars.atlassian.net/browse/MANTA-30670</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>31073</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>MANTA-30667</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Manta</t>
+        </is>
+      </c>
+      <c r="C5" s="1" t="inlineStr">
+        <is>
+          <t>https://carboncars.atlassian.net/browse/MANTA-30667</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>31070</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>MANTA-30650</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Manta</t>
+        </is>
+      </c>
+      <c r="C6" s="1" t="inlineStr">
+        <is>
+          <t>https://carboncars.atlassian.net/browse/MANTA-30650</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>31055</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>MANTA-30636</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Manta</t>
+        </is>
+      </c>
+      <c r="C7" s="1" t="inlineStr">
+        <is>
+          <t>https://carboncars.atlassian.net/browse/MANTA-30636</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>31041</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>MANTA-30543</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Manta</t>
+        </is>
+      </c>
+      <c r="C8" s="1" t="inlineStr">
+        <is>
+          <t>https://carboncars.atlassian.net/browse/MANTA-30543</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>30949</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>MANTA-30520</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Manta</t>
+        </is>
+      </c>
+      <c r="C9" s="1" t="inlineStr">
+        <is>
+          <t>https://carboncars.atlassian.net/browse/MANTA-30520</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>30929</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>MANTA-30496</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Manta</t>
+        </is>
+      </c>
+      <c r="C10" s="1" t="inlineStr">
+        <is>
+          <t>https://carboncars.atlassian.net/browse/MANTA-30496</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>30905</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>MANTA-30494</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Manta</t>
+        </is>
+      </c>
+      <c r="C11" s="1" t="inlineStr">
+        <is>
+          <t>https://carboncars.atlassian.net/browse/MANTA-30494</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>30903</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>MANTA-30458</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Manta</t>
+        </is>
+      </c>
+      <c r="C12" s="1" t="inlineStr">
+        <is>
+          <t>https://carboncars.atlassian.net/browse/MANTA-30458</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>30871</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>MANTA-30447</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Manta</t>
+        </is>
+      </c>
+      <c r="C13" s="1" t="inlineStr">
+        <is>
+          <t>https://carboncars.atlassian.net/browse/MANTA-30447</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>30860</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>MANTA-30435</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Manta</t>
+        </is>
+      </c>
+      <c r="C14" s="1" t="inlineStr">
+        <is>
+          <t>https://carboncars.atlassian.net/browse/MANTA-30435</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>30848</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>MANTA-30419</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Manta</t>
+        </is>
+      </c>
+      <c r="C15" s="1" t="inlineStr">
+        <is>
+          <t>https://carboncars.atlassian.net/browse/MANTA-30419</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>30832</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>MANTA-30403</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Manta</t>
+        </is>
+      </c>
+      <c r="C16" s="1" t="inlineStr">
+        <is>
+          <t>https://carboncars.atlassian.net/browse/MANTA-30403</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>30816</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>MANTA-30346</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Manta</t>
+        </is>
+      </c>
+      <c r="C17" s="1" t="inlineStr">
+        <is>
+          <t>https://carboncars.atlassian.net/browse/MANTA-30346</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>30766</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>MANTA-30265</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Manta</t>
+        </is>
+      </c>
+      <c r="C18" s="1" t="inlineStr">
+        <is>
+          <t>https://carboncars.atlassian.net/browse/MANTA-30265</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>30693</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>MANTA-30099</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Manta</t>
+        </is>
+      </c>
+      <c r="C19" s="1" t="inlineStr">
+        <is>
+          <t>https://carboncars.atlassian.net/browse/MANTA-30099</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>30556</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>MANTA-30072</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Manta</t>
+        </is>
+      </c>
+      <c r="C20" s="1" t="inlineStr">
+        <is>
+          <t>https://carboncars.atlassian.net/browse/MANTA-30072</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>30529</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>MANTA-30053</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Manta</t>
+        </is>
+      </c>
+      <c r="C21" s="1" t="inlineStr">
+        <is>
+          <t>https://carboncars.atlassian.net/browse/MANTA-30053</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>30510</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C21" r:id="rId20"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/src/data_update/update_cards.xlsx
+++ b/src/data_update/update_cards.xlsx
@@ -423,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H4"/>
+  <dimension ref="A1:H5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="6" max="6"/>
@@ -474,44 +474,44 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>MANTA-29977</t>
+          <t>TENSYLON-675</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Manta</t>
+          <t>Tensylon</t>
         </is>
       </c>
       <c r="C2" s="1" t="inlineStr">
         <is>
-          <t>https://carboncars.atlassian.net/browse/MANTA-29977</t>
+          <t>https://carboncars.atlassian.net/browse/TENSYLON-675</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>30442</t>
+          <t>30282</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Liberado Engenharia</t>
+          <t>A Produzir</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>⚪️REC. Encaminhado</t>
+          <t>🟢REC. Liberado</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>GWM - TANK 300 SUV - 2026</t>
+          <t>MERCEDES-BENZ - EQS 450+ SUV - 2024</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>MANTA-29549</t>
+          <t>MANTA-29977</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -521,12 +521,12 @@
       </c>
       <c r="C3" s="1" t="inlineStr">
         <is>
-          <t>https://carboncars.atlassian.net/browse/MANTA-29549</t>
+          <t>https://carboncars.atlassian.net/browse/MANTA-29977</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>30059</t>
+          <t>30442</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -541,42 +541,79 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>BMW - X1 SUV - 2026</t>
+          <t>GWM - TANK 300 SUV - 2026</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
+          <t>MANTA-29549</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Manta</t>
+        </is>
+      </c>
+      <c r="C4" s="1" t="inlineStr">
+        <is>
+          <t>https://carboncars.atlassian.net/browse/MANTA-29549</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>30059</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Liberado Engenharia</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>⚪️REC. Encaminhado</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>BMW - X1 SUV - 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
           <t>MANTA-28595</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="B5" t="inlineStr">
         <is>
           <t>Manta</t>
         </is>
       </c>
-      <c r="C4" s="1" t="inlineStr">
+      <c r="C5" s="1" t="inlineStr">
         <is>
           <t>https://carboncars.atlassian.net/browse/MANTA-28595</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="D5" t="inlineStr">
         <is>
           <t>29222</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
+      <c r="E5" t="inlineStr">
         <is>
           <t>Liberado Engenharia</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
+      <c r="F5" t="inlineStr">
         <is>
           <t>⚪️REC. Encaminhado</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
+      <c r="G5" t="inlineStr">
         <is>
           <t>TOYOTA - COROLLA SEDAN - 2025</t>
         </is>
@@ -587,6 +624,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C3" r:id="rId2"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C5" r:id="rId4"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/src/data_update/update_cards.xlsx
+++ b/src/data_update/update_cards.xlsx
@@ -17,19 +17,12 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <color theme="10"/>
-      <sz val="12"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -50,17 +43,14 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="1"/>
   </cellXfs>
-  <cellStyles count="2">
+  <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
-    <cellStyle name="Hyperlink" xfId="1" builtinId="8" hidden="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
@@ -423,11 +413,8 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H5"/>
+  <dimension ref="A1:H1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="11" customWidth="1" min="6" max="6"/>
-  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
@@ -471,161 +458,7 @@
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>TENSYLON-675</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>Tensylon</t>
-        </is>
-      </c>
-      <c r="C2" s="1" t="inlineStr">
-        <is>
-          <t>https://carboncars.atlassian.net/browse/TENSYLON-675</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>30282</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>A Produzir</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>🟢REC. Liberado</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>MERCEDES-BENZ - EQS 450+ SUV - 2024</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>MANTA-29977</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>Manta</t>
-        </is>
-      </c>
-      <c r="C3" s="1" t="inlineStr">
-        <is>
-          <t>https://carboncars.atlassian.net/browse/MANTA-29977</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>30442</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>Liberado Engenharia</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>⚪️REC. Encaminhado</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>GWM - TANK 300 SUV - 2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>MANTA-29549</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Manta</t>
-        </is>
-      </c>
-      <c r="C4" s="1" t="inlineStr">
-        <is>
-          <t>https://carboncars.atlassian.net/browse/MANTA-29549</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>30059</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>Liberado Engenharia</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>⚪️REC. Encaminhado</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>BMW - X1 SUV - 2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>MANTA-28595</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>Manta</t>
-        </is>
-      </c>
-      <c r="C5" s="1" t="inlineStr">
-        <is>
-          <t>https://carboncars.atlassian.net/browse/MANTA-28595</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>29222</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>Liberado Engenharia</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>⚪️REC. Encaminhado</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>TOYOTA - COROLLA SEDAN - 2025</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <hyperlinks>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C2" r:id="rId1"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C3" r:id="rId2"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C4" r:id="rId3"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C5" r:id="rId4"/>
-  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>